--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -620,10 +620,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>41.67</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -707,13 +707,13 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
         <v>12</v>
       </c>
       <c r="AI2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -731,10 +731,10 @@
         <v>3567</v>
       </c>
       <c r="D3" t="n">
-        <v>2482</v>
+        <v>2771</v>
       </c>
       <c r="E3" t="n">
-        <v>69.58</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -743,88 +743,88 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1516</v>
+        <v>1281</v>
       </c>
       <c r="I3" t="n">
-        <v>1858</v>
+        <v>1819</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>4044</v>
+        <v>4118</v>
       </c>
       <c r="S3" t="n">
-        <v>2491</v>
+        <v>2798</v>
       </c>
       <c r="T3" t="n">
-        <v>1491</v>
+        <v>1283</v>
       </c>
       <c r="U3" t="n">
-        <v>1763</v>
+        <v>1819</v>
       </c>
       <c r="V3" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="W3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4054</v>
+        <v>4118</v>
       </c>
       <c r="AE3" t="n">
-        <v>2515</v>
+        <v>2795</v>
       </c>
       <c r="AF3" t="n">
-        <v>-477</v>
+        <v>-551</v>
       </c>
       <c r="AG3" t="n">
-        <v>-9</v>
+        <v>-27</v>
       </c>
       <c r="AH3" t="n">
-        <v>-487</v>
+        <v>-551</v>
       </c>
       <c r="AI3" t="n">
-        <v>-33</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="4">
@@ -842,100 +842,100 @@
         <v>1264</v>
       </c>
       <c r="D4" t="n">
-        <v>610</v>
+        <v>657</v>
       </c>
       <c r="E4" t="n">
-        <v>48.26</v>
+        <v>51.98</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>16.67</v>
+        <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="I4" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="S4" t="n">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="T4" t="n">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="U4" t="n">
-        <v>514</v>
+        <v>446</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AE4" t="n">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="AF4" t="n">
-        <v>-144</v>
+        <v>-146</v>
       </c>
       <c r="AG4" t="n">
         <v>-4</v>
       </c>
       <c r="AH4" t="n">
-        <v>-144</v>
+        <v>-146</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="5">
@@ -953,34 +953,34 @@
         <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>3697</v>
+        <v>4295</v>
       </c>
       <c r="E5" t="n">
-        <v>76.06999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2208</v>
+        <v>1831</v>
       </c>
       <c r="I5" t="n">
-        <v>3449</v>
+        <v>3389</v>
       </c>
       <c r="J5" t="n">
-        <v>92</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -989,34 +989,34 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6152</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4225</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1756</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3456</v>
+      </c>
+      <c r="V5" t="n">
+        <v>386</v>
+      </c>
+      <c r="W5" t="n">
         <v>95</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6010</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3715</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2208</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3445</v>
-      </c>
-      <c r="V5" t="n">
-        <v>96</v>
-      </c>
-      <c r="W5" t="n">
-        <v>88</v>
-      </c>
       <c r="X5" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1025,28 +1025,28 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>422</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6010</v>
+        <v>6181</v>
       </c>
       <c r="AE5" t="n">
-        <v>3714</v>
+        <v>4330</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1150</v>
+        <v>-1292</v>
       </c>
       <c r="AG5" t="n">
-        <v>-18</v>
+        <v>70</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1150</v>
+        <v>-1321</v>
       </c>
       <c r="AI5" t="n">
-        <v>-17</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="6">
@@ -1064,10 +1064,10 @@
         <v>2537</v>
       </c>
       <c r="D6" t="n">
-        <v>1983</v>
+        <v>2202</v>
       </c>
       <c r="E6" t="n">
-        <v>78.16</v>
+        <v>86.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="I6" t="n">
-        <v>1615</v>
+        <v>1675</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1094,31 +1094,31 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="S6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="T6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="U6" t="n">
-        <v>1620</v>
+        <v>1675</v>
       </c>
       <c r="V6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1130,34 +1130,34 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="AE6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="AF6" t="n">
-        <v>-521</v>
+        <v>-584</v>
       </c>
       <c r="AG6" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="AH6" t="n">
-        <v>-521</v>
+        <v>-584</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="7">
@@ -1175,10 +1175,10 @@
         <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>652</v>
       </c>
       <c r="E7" t="n">
-        <v>57.49</v>
+        <v>68.27</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1187,88 +1187,88 @@
         <v>4.88</v>
       </c>
       <c r="H7" t="n">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="I7" t="n">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1121</v>
+      </c>
+      <c r="S7" t="n">
+        <v>659</v>
+      </c>
+      <c r="T7" t="n">
+        <v>449</v>
+      </c>
+      <c r="U7" t="n">
+        <v>544</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1105</v>
-      </c>
-      <c r="S7" t="n">
-        <v>550</v>
-      </c>
-      <c r="T7" t="n">
-        <v>543</v>
-      </c>
-      <c r="U7" t="n">
-        <v>490</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
       <c r="W7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="AE7" t="n">
-        <v>549</v>
+        <v>658</v>
       </c>
       <c r="AF7" t="n">
-        <v>-150</v>
+        <v>-166</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="AH7" t="n">
-        <v>-150</v>
+        <v>-166</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="8">
@@ -1286,10 +1286,10 @@
         <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>565</v>
+        <v>614</v>
       </c>
       <c r="E8" t="n">
-        <v>71.43000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="I8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1322,34 +1322,34 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="S8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="T8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="U8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1358,28 +1358,28 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="AE8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="AF8" t="n">
-        <v>-206</v>
+        <v>-227</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="AH8" t="n">
-        <v>-206</v>
+        <v>-227</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="9">
@@ -1397,10 +1397,10 @@
         <v>3701</v>
       </c>
       <c r="D9" t="n">
-        <v>2286</v>
+        <v>2424</v>
       </c>
       <c r="E9" t="n">
-        <v>61.77</v>
+        <v>65.5</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1409,22 +1409,22 @@
         <v>4.76</v>
       </c>
       <c r="H9" t="n">
-        <v>2210</v>
+        <v>2105</v>
       </c>
       <c r="I9" t="n">
-        <v>2073</v>
+        <v>1928</v>
       </c>
       <c r="J9" t="n">
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1433,34 +1433,34 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4573</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2432</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1928</v>
+      </c>
+      <c r="V9" t="n">
+        <v>229</v>
+      </c>
+      <c r="W9" t="n">
+        <v>36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4540</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2305</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2210</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2074</v>
-      </c>
-      <c r="V9" t="n">
-        <v>155</v>
-      </c>
-      <c r="W9" t="n">
-        <v>27</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>2</v>
@@ -1469,28 +1469,28 @@
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>61</v>
+        <v>261</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>4539</v>
+        <v>4574</v>
       </c>
       <c r="AE9" t="n">
-        <v>2302</v>
+        <v>2438</v>
       </c>
       <c r="AF9" t="n">
-        <v>-839</v>
+        <v>-872</v>
       </c>
       <c r="AG9" t="n">
-        <v>-19</v>
+        <v>-8</v>
       </c>
       <c r="AH9" t="n">
-        <v>-838</v>
+        <v>-873</v>
       </c>
       <c r="AI9" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="10">
@@ -1508,100 +1508,100 @@
         <v>4982</v>
       </c>
       <c r="D10" t="n">
-        <v>2761</v>
+        <v>3016</v>
       </c>
       <c r="E10" t="n">
-        <v>55.42</v>
+        <v>60.54</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.46</v>
+        <v>7.54</v>
       </c>
       <c r="H10" t="n">
-        <v>3079</v>
+        <v>2889</v>
       </c>
       <c r="I10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="J10" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="S10" t="n">
-        <v>2772</v>
+        <v>3042</v>
       </c>
       <c r="T10" t="n">
-        <v>3079</v>
+        <v>2890</v>
       </c>
       <c r="U10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="V10" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="W10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="X10" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="AE10" t="n">
-        <v>2772</v>
+        <v>3040</v>
       </c>
       <c r="AF10" t="n">
-        <v>-902</v>
+        <v>-987</v>
       </c>
       <c r="AG10" t="n">
-        <v>-11</v>
+        <v>-26</v>
       </c>
       <c r="AH10" t="n">
-        <v>-902</v>
+        <v>-987</v>
       </c>
       <c r="AI10" t="n">
-        <v>-11</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="11">
@@ -1619,31 +1619,31 @@
         <v>6920</v>
       </c>
       <c r="D11" t="n">
-        <v>3868</v>
+        <v>4194</v>
       </c>
       <c r="E11" t="n">
-        <v>55.9</v>
+        <v>60.61</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13.28</v>
+        <v>9.17</v>
       </c>
       <c r="H11" t="n">
-        <v>3915</v>
+        <v>3660</v>
       </c>
       <c r="I11" t="n">
-        <v>3813</v>
+        <v>3861</v>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1655,31 +1655,31 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="S11" t="n">
-        <v>3900</v>
+        <v>4199</v>
       </c>
       <c r="T11" t="n">
-        <v>3918</v>
+        <v>3661</v>
       </c>
       <c r="U11" t="n">
-        <v>3813</v>
+        <v>3854</v>
       </c>
       <c r="V11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="W11" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="AC11" t="n">
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="AE11" t="n">
-        <v>3900</v>
+        <v>4198</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1024</v>
+        <v>-1089</v>
       </c>
       <c r="AG11" t="n">
-        <v>-32</v>
+        <v>-5</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1024</v>
+        <v>-1089</v>
       </c>
       <c r="AI11" t="n">
-        <v>-32</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="12">
@@ -1730,34 +1730,34 @@
         <v>4605</v>
       </c>
       <c r="D12" t="n">
-        <v>2585</v>
+        <v>2858</v>
       </c>
       <c r="E12" t="n">
-        <v>56.13</v>
+        <v>62.06</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>19.35</v>
+        <v>7.53</v>
       </c>
       <c r="H12" t="n">
-        <v>2373</v>
+        <v>2154</v>
       </c>
       <c r="I12" t="n">
-        <v>2316</v>
+        <v>2397</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="K12" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1766,34 +1766,34 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="S12" t="n">
-        <v>2591</v>
+        <v>2880</v>
       </c>
       <c r="T12" t="n">
-        <v>2373</v>
+        <v>2159</v>
       </c>
       <c r="U12" t="n">
-        <v>2314</v>
+        <v>2397</v>
       </c>
       <c r="V12" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="W12" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="X12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>3</v>
@@ -1802,28 +1802,28 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="AE12" t="n">
-        <v>2591</v>
+        <v>2874</v>
       </c>
       <c r="AF12" t="n">
-        <v>-514</v>
+        <v>-557</v>
       </c>
       <c r="AG12" t="n">
-        <v>-6</v>
+        <v>-22</v>
       </c>
       <c r="AH12" t="n">
-        <v>-514</v>
+        <v>-557</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="13">
@@ -1841,100 +1841,100 @@
         <v>2209</v>
       </c>
       <c r="D13" t="n">
-        <v>1070</v>
+        <v>1208</v>
       </c>
       <c r="E13" t="n">
-        <v>48.44</v>
+        <v>54.69</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>11.85</v>
+        <v>6.85</v>
       </c>
       <c r="H13" t="n">
-        <v>1273</v>
+        <v>1148</v>
       </c>
       <c r="I13" t="n">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="J13" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="S13" t="n">
-        <v>1080</v>
+        <v>1216</v>
       </c>
       <c r="T13" t="n">
-        <v>1274</v>
+        <v>1150</v>
       </c>
       <c r="U13" t="n">
-        <v>901</v>
+        <v>800</v>
       </c>
       <c r="V13" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="W13" t="n">
         <v>30</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="AE13" t="n">
-        <v>1079</v>
+        <v>1216</v>
       </c>
       <c r="AF13" t="n">
-        <v>-174</v>
+        <v>-187</v>
       </c>
       <c r="AG13" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AH13" t="n">
-        <v>-174</v>
+        <v>-187</v>
       </c>
       <c r="AI13" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="14">
@@ -1952,100 +1952,100 @@
         <v>7057</v>
       </c>
       <c r="D14" t="n">
-        <v>5351</v>
+        <v>5997</v>
       </c>
       <c r="E14" t="n">
-        <v>75.83</v>
+        <v>84.98</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>12.28</v>
+        <v>11.43</v>
       </c>
       <c r="H14" t="n">
-        <v>3667</v>
+        <v>3161</v>
       </c>
       <c r="I14" t="n">
-        <v>5078</v>
+        <v>5121</v>
       </c>
       <c r="J14" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="L14" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>9254</v>
+        <v>9452</v>
       </c>
       <c r="S14" t="n">
-        <v>5465</v>
+        <v>6129</v>
       </c>
       <c r="T14" t="n">
-        <v>3402</v>
+        <v>2895</v>
       </c>
       <c r="U14" t="n">
-        <v>5075</v>
+        <v>5121</v>
       </c>
       <c r="V14" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="W14" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>8899</v>
+        <v>9097</v>
       </c>
       <c r="AE14" t="n">
-        <v>5376</v>
+        <v>6041</v>
       </c>
       <c r="AF14" t="n">
-        <v>-2197</v>
+        <v>-2395</v>
       </c>
       <c r="AG14" t="n">
-        <v>-114</v>
+        <v>-132</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1842</v>
+        <v>-2040</v>
       </c>
       <c r="AI14" t="n">
-        <v>-25</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2063,10 @@
         <v>911</v>
       </c>
       <c r="D15" t="n">
-        <v>762</v>
+        <v>826</v>
       </c>
       <c r="E15" t="n">
-        <v>83.64</v>
+        <v>90.67</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2075,19 +2075,19 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="I15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2099,31 +2099,31 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="S15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="T15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="V15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2135,28 +2135,28 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="AE15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="AF15" t="n">
-        <v>-229</v>
+        <v>-241</v>
       </c>
       <c r="AG15" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="AH15" t="n">
-        <v>-229</v>
+        <v>-241</v>
       </c>
       <c r="AI15" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="16">
@@ -2174,10 +2174,10 @@
         <v>452</v>
       </c>
       <c r="D16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="E16" t="n">
-        <v>80.97</v>
+        <v>86.28</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2186,16 +2186,16 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="S16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="T16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="U16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
         <v>2</v>
@@ -2252,19 +2252,19 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="AE16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="AF16" t="n">
-        <v>-149</v>
+        <v>-170</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-149</v>
+        <v>-170</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2285,10 +2285,10 @@
         <v>2416</v>
       </c>
       <c r="D17" t="n">
-        <v>1387</v>
+        <v>1538</v>
       </c>
       <c r="E17" t="n">
-        <v>57.41</v>
+        <v>63.66</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2297,85 +2297,85 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1347</v>
+        <v>1236</v>
       </c>
       <c r="I17" t="n">
-        <v>1255</v>
+        <v>1149</v>
       </c>
       <c r="J17" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2753</v>
+        <v>2781</v>
       </c>
       <c r="S17" t="n">
-        <v>1400</v>
+        <v>1541</v>
       </c>
       <c r="T17" t="n">
-        <v>1348</v>
+        <v>1230</v>
       </c>
       <c r="U17" t="n">
-        <v>1255</v>
+        <v>1127</v>
       </c>
       <c r="V17" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2753</v>
+        <v>2784</v>
       </c>
       <c r="AE17" t="n">
-        <v>1399</v>
+        <v>1550</v>
       </c>
       <c r="AF17" t="n">
-        <v>-337</v>
+        <v>-365</v>
       </c>
       <c r="AG17" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="AH17" t="n">
-        <v>-337</v>
+        <v>-368</v>
       </c>
       <c r="AI17" t="n">
         <v>-12</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,177 +417,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -731,10 +719,10 @@
         <v>3567</v>
       </c>
       <c r="D3" t="n">
-        <v>2771</v>
+        <v>2916</v>
       </c>
       <c r="E3" t="n">
-        <v>77.68000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -743,19 +731,19 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1281</v>
+        <v>1169</v>
       </c>
       <c r="I3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="J3" t="n">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -773,25 +761,25 @@
         <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="S3" t="n">
-        <v>2798</v>
+        <v>2924</v>
       </c>
       <c r="T3" t="n">
-        <v>1283</v>
+        <v>1169</v>
       </c>
       <c r="U3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="V3" t="n">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -809,22 +797,22 @@
         <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="AE3" t="n">
-        <v>2795</v>
+        <v>2924</v>
       </c>
       <c r="AF3" t="n">
-        <v>-551</v>
+        <v>-563</v>
       </c>
       <c r="AG3" t="n">
-        <v>-27</v>
+        <v>-8</v>
       </c>
       <c r="AH3" t="n">
-        <v>-551</v>
+        <v>-563</v>
       </c>
       <c r="AI3" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="4">
@@ -842,10 +830,10 @@
         <v>1264</v>
       </c>
       <c r="D4" t="n">
-        <v>657</v>
+        <v>718</v>
       </c>
       <c r="E4" t="n">
-        <v>51.98</v>
+        <v>56.8</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -854,52 +842,52 @@
         <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="I4" t="n">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="S4" t="n">
-        <v>661</v>
+        <v>744</v>
       </c>
       <c r="T4" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="U4" t="n">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="W4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -908,34 +896,34 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="AE4" t="n">
-        <v>670</v>
+        <v>744</v>
       </c>
       <c r="AF4" t="n">
-        <v>-146</v>
+        <v>-156</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4</v>
+        <v>-26</v>
       </c>
       <c r="AH4" t="n">
-        <v>-146</v>
+        <v>-156</v>
       </c>
       <c r="AI4" t="n">
-        <v>-13</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="5">
@@ -953,34 +941,34 @@
         <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>4295</v>
+        <v>4525</v>
       </c>
       <c r="E5" t="n">
-        <v>88.37</v>
+        <v>93.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1831</v>
+        <v>1605</v>
       </c>
       <c r="I5" t="n">
-        <v>3389</v>
+        <v>3789</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -989,34 +977,34 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>6152</v>
+        <v>6241</v>
       </c>
       <c r="S5" t="n">
-        <v>4225</v>
+        <v>4550</v>
       </c>
       <c r="T5" t="n">
-        <v>1756</v>
+        <v>1605</v>
       </c>
       <c r="U5" t="n">
-        <v>3456</v>
+        <v>3789</v>
       </c>
       <c r="V5" t="n">
-        <v>386</v>
+        <v>104</v>
       </c>
       <c r="W5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="X5" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1025,28 +1013,28 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6181</v>
+        <v>6240</v>
       </c>
       <c r="AE5" t="n">
-        <v>4330</v>
+        <v>4550</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1292</v>
+        <v>-1381</v>
       </c>
       <c r="AG5" t="n">
-        <v>70</v>
+        <v>-25</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1321</v>
+        <v>-1380</v>
       </c>
       <c r="AI5" t="n">
-        <v>-35</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="6">
@@ -1064,10 +1052,10 @@
         <v>2537</v>
       </c>
       <c r="D6" t="n">
-        <v>2202</v>
+        <v>2343</v>
       </c>
       <c r="E6" t="n">
-        <v>86.8</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1076,19 +1064,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>902</v>
+        <v>805</v>
       </c>
       <c r="I6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="J6" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1106,25 +1094,25 @@
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="S6" t="n">
-        <v>2219</v>
+        <v>2353</v>
       </c>
       <c r="T6" t="n">
-        <v>902</v>
+        <v>806</v>
       </c>
       <c r="U6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="V6" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1142,22 +1130,22 @@
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="AE6" t="n">
-        <v>2219</v>
+        <v>2352</v>
       </c>
       <c r="AF6" t="n">
-        <v>-584</v>
+        <v>-621</v>
       </c>
       <c r="AG6" t="n">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="AH6" t="n">
-        <v>-584</v>
+        <v>-621</v>
       </c>
       <c r="AI6" t="n">
-        <v>-17</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="7">
@@ -1175,10 +1163,10 @@
         <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="E7" t="n">
-        <v>68.27</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1187,19 +1175,19 @@
         <v>4.88</v>
       </c>
       <c r="H7" t="n">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="I7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1217,25 +1205,25 @@
         <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="S7" t="n">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="T7" t="n">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="U7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="W7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1253,22 +1241,22 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="AE7" t="n">
-        <v>658</v>
+        <v>692</v>
       </c>
       <c r="AF7" t="n">
-        <v>-166</v>
+        <v>-179</v>
       </c>
       <c r="AG7" t="n">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="AH7" t="n">
-        <v>-166</v>
+        <v>-179</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="8">
@@ -1286,10 +1274,10 @@
         <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="E8" t="n">
-        <v>77.62</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1298,25 +1286,25 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="I8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1328,31 +1316,31 @@
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="S8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="T8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="U8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1364,22 +1352,22 @@
         <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AE8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AF8" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="AG8" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="AI8" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1397,34 +1385,34 @@
         <v>3701</v>
       </c>
       <c r="D9" t="n">
-        <v>2424</v>
+        <v>2493</v>
       </c>
       <c r="E9" t="n">
-        <v>65.5</v>
+        <v>67.36</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.76</v>
+        <v>6.17</v>
       </c>
       <c r="H9" t="n">
-        <v>2105</v>
+        <v>2049</v>
       </c>
       <c r="I9" t="n">
-        <v>1928</v>
+        <v>1986</v>
       </c>
       <c r="J9" t="n">
         <v>223</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1433,34 +1421,34 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="Q9" t="n">
         <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>4573</v>
+        <v>4596</v>
       </c>
       <c r="S9" t="n">
-        <v>2432</v>
+        <v>2510</v>
       </c>
       <c r="T9" t="n">
-        <v>2100</v>
+        <v>2049</v>
       </c>
       <c r="U9" t="n">
-        <v>1928</v>
+        <v>1990</v>
       </c>
       <c r="V9" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="W9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>2</v>
@@ -1469,28 +1457,28 @@
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AC9" t="n">
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>4574</v>
+        <v>4596</v>
       </c>
       <c r="AE9" t="n">
-        <v>2438</v>
+        <v>2510</v>
       </c>
       <c r="AF9" t="n">
-        <v>-872</v>
+        <v>-895</v>
       </c>
       <c r="AG9" t="n">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="AH9" t="n">
-        <v>-873</v>
+        <v>-895</v>
       </c>
       <c r="AI9" t="n">
-        <v>-14</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="10">
@@ -1508,100 +1496,100 @@
         <v>4982</v>
       </c>
       <c r="D10" t="n">
-        <v>3016</v>
+        <v>3125</v>
       </c>
       <c r="E10" t="n">
-        <v>60.54</v>
+        <v>62.73</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>7.54</v>
+        <v>9.629999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2889</v>
+        <v>2813</v>
       </c>
       <c r="I10" t="n">
-        <v>2279</v>
+        <v>2427</v>
       </c>
       <c r="J10" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="S10" t="n">
-        <v>3042</v>
+        <v>3149</v>
       </c>
       <c r="T10" t="n">
-        <v>2890</v>
+        <v>2808</v>
       </c>
       <c r="U10" t="n">
-        <v>2279</v>
+        <v>2424</v>
       </c>
       <c r="V10" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="W10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="AE10" t="n">
-        <v>3040</v>
+        <v>3152</v>
       </c>
       <c r="AF10" t="n">
-        <v>-987</v>
+        <v>-1015</v>
       </c>
       <c r="AG10" t="n">
-        <v>-26</v>
+        <v>-24</v>
       </c>
       <c r="AH10" t="n">
-        <v>-987</v>
+        <v>-1015</v>
       </c>
       <c r="AI10" t="n">
-        <v>-24</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="11">
@@ -1619,31 +1607,31 @@
         <v>6920</v>
       </c>
       <c r="D11" t="n">
-        <v>4194</v>
+        <v>4339</v>
       </c>
       <c r="E11" t="n">
-        <v>60.61</v>
+        <v>62.7</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>9.17</v>
+        <v>7.27</v>
       </c>
       <c r="H11" t="n">
-        <v>3660</v>
+        <v>3560</v>
       </c>
       <c r="I11" t="n">
-        <v>3861</v>
+        <v>3868</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1655,31 +1643,31 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="S11" t="n">
-        <v>4199</v>
+        <v>4368</v>
       </c>
       <c r="T11" t="n">
-        <v>3661</v>
+        <v>3560</v>
       </c>
       <c r="U11" t="n">
-        <v>3854</v>
+        <v>3868</v>
       </c>
       <c r="V11" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="W11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1691,28 +1679,28 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>227</v>
+        <v>456</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="AE11" t="n">
-        <v>4198</v>
+        <v>4368</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1089</v>
+        <v>-1144</v>
       </c>
       <c r="AG11" t="n">
-        <v>-5</v>
+        <v>-29</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1089</v>
+        <v>-1144</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="12">
@@ -1730,37 +1718,37 @@
         <v>4605</v>
       </c>
       <c r="D12" t="n">
-        <v>2858</v>
+        <v>2969</v>
       </c>
       <c r="E12" t="n">
-        <v>62.06</v>
+        <v>64.47</v>
       </c>
       <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2077</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2487</v>
+      </c>
+      <c r="J12" t="n">
+        <v>73</v>
+      </c>
+      <c r="K12" t="n">
+        <v>117</v>
+      </c>
+      <c r="L12" t="n">
+        <v>43</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2154</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2397</v>
-      </c>
-      <c r="J12" t="n">
-        <v>58</v>
-      </c>
-      <c r="K12" t="n">
-        <v>128</v>
-      </c>
-      <c r="L12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1772,31 +1760,31 @@
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="S12" t="n">
-        <v>2880</v>
+        <v>2983</v>
       </c>
       <c r="T12" t="n">
-        <v>2159</v>
+        <v>2077</v>
       </c>
       <c r="U12" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="V12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="W12" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="X12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1808,22 +1796,22 @@
         <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="AE12" t="n">
-        <v>2874</v>
+        <v>2983</v>
       </c>
       <c r="AF12" t="n">
-        <v>-557</v>
+        <v>-572</v>
       </c>
       <c r="AG12" t="n">
-        <v>-22</v>
+        <v>-14</v>
       </c>
       <c r="AH12" t="n">
-        <v>-557</v>
+        <v>-572</v>
       </c>
       <c r="AI12" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="13">
@@ -1841,34 +1829,34 @@
         <v>2209</v>
       </c>
       <c r="D13" t="n">
-        <v>1208</v>
+        <v>1255</v>
       </c>
       <c r="E13" t="n">
-        <v>54.69</v>
+        <v>56.81</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.85</v>
+        <v>11.34</v>
       </c>
       <c r="H13" t="n">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="I13" t="n">
-        <v>800</v>
+        <v>844</v>
       </c>
       <c r="J13" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="K13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
@@ -1877,34 +1865,34 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13" t="n">
         <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="S13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="T13" t="n">
-        <v>1150</v>
+        <v>1115</v>
       </c>
       <c r="U13" t="n">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="V13" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="W13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="X13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>3</v>
@@ -1913,28 +1901,28 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AC13" t="n">
         <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="AE13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="AF13" t="n">
-        <v>-187</v>
+        <v>-197</v>
       </c>
       <c r="AG13" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="AH13" t="n">
-        <v>-187</v>
+        <v>-197</v>
       </c>
       <c r="AI13" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">
@@ -1952,34 +1940,34 @@
         <v>7057</v>
       </c>
       <c r="D14" t="n">
-        <v>5997</v>
+        <v>6365</v>
       </c>
       <c r="E14" t="n">
-        <v>84.98</v>
+        <v>90.19</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>11.43</v>
+        <v>12.28</v>
       </c>
       <c r="H14" t="n">
-        <v>3161</v>
+        <v>2948</v>
       </c>
       <c r="I14" t="n">
-        <v>5121</v>
+        <v>5564</v>
       </c>
       <c r="J14" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -1988,34 +1976,34 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>9452</v>
+        <v>9558</v>
       </c>
       <c r="S14" t="n">
-        <v>6129</v>
+        <v>6511</v>
       </c>
       <c r="T14" t="n">
-        <v>2895</v>
+        <v>2682</v>
       </c>
       <c r="U14" t="n">
-        <v>5121</v>
+        <v>5561</v>
       </c>
       <c r="V14" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="W14" t="n">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>11</v>
@@ -2024,28 +2012,28 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>9097</v>
+        <v>9203</v>
       </c>
       <c r="AE14" t="n">
-        <v>6041</v>
+        <v>6424</v>
       </c>
       <c r="AF14" t="n">
-        <v>-2395</v>
+        <v>-2501</v>
       </c>
       <c r="AG14" t="n">
-        <v>-132</v>
+        <v>-146</v>
       </c>
       <c r="AH14" t="n">
-        <v>-2040</v>
+        <v>-2146</v>
       </c>
       <c r="AI14" t="n">
-        <v>-44</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2051,10 @@
         <v>911</v>
       </c>
       <c r="D15" t="n">
-        <v>826</v>
+        <v>868</v>
       </c>
       <c r="E15" t="n">
-        <v>90.67</v>
+        <v>95.28</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2075,13 +2063,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="I15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2105,19 +2093,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="S15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="T15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="U15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2141,22 +2129,22 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AE15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="AF15" t="n">
-        <v>-241</v>
+        <v>-244</v>
       </c>
       <c r="AG15" t="n">
-        <v>-7</v>
+        <v>-18</v>
       </c>
       <c r="AH15" t="n">
-        <v>-241</v>
+        <v>-244</v>
       </c>
       <c r="AI15" t="n">
-        <v>-7</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="16">
@@ -2174,10 +2162,10 @@
         <v>452</v>
       </c>
       <c r="D16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E16" t="n">
-        <v>86.28</v>
+        <v>87.17</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2186,19 +2174,19 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="J16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2213,28 +2201,28 @@
         <v>20</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>622</v>
       </c>
       <c r="S16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="T16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="U16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="V16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2249,13 +2237,13 @@
         <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>622</v>
       </c>
       <c r="AE16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AF16" t="n">
         <v>-170</v>
@@ -2285,10 +2273,10 @@
         <v>2416</v>
       </c>
       <c r="D17" t="n">
-        <v>1538</v>
+        <v>1615</v>
       </c>
       <c r="E17" t="n">
-        <v>63.66</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2297,88 +2285,88 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1236</v>
+        <v>1162</v>
       </c>
       <c r="I17" t="n">
-        <v>1149</v>
+        <v>1195</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2781</v>
+        <v>2805</v>
       </c>
       <c r="S17" t="n">
-        <v>1541</v>
+        <v>1640</v>
       </c>
       <c r="T17" t="n">
-        <v>1230</v>
+        <v>1163</v>
       </c>
       <c r="U17" t="n">
-        <v>1127</v>
+        <v>1195</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AC17" t="n">
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2784</v>
+        <v>2804</v>
       </c>
       <c r="AE17" t="n">
-        <v>1550</v>
+        <v>1638</v>
       </c>
       <c r="AF17" t="n">
-        <v>-365</v>
+        <v>-389</v>
       </c>
       <c r="AG17" t="n">
-        <v>-3</v>
+        <v>-25</v>
       </c>
       <c r="AH17" t="n">
-        <v>-368</v>
+        <v>-388</v>
       </c>
       <c r="AI17" t="n">
-        <v>-12</v>
+        <v>-23</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -608,16 +608,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>41.67</v>
+        <v>58.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>12</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         <v>3567</v>
       </c>
       <c r="D3" t="n">
-        <v>2916</v>
+        <v>3626</v>
       </c>
       <c r="E3" t="n">
-        <v>81.75</v>
+        <v>101.65</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -731,88 +731,88 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="I3" t="n">
-        <v>2221</v>
+        <v>2752</v>
       </c>
       <c r="J3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="S3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
       <c r="T3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="U3" t="n">
-        <v>2221</v>
+        <v>2754</v>
       </c>
       <c r="V3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="W3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="AE3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
       <c r="AF3" t="n">
-        <v>-563</v>
+        <v>-691</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8</v>
+        <v>66</v>
       </c>
       <c r="AH3" t="n">
-        <v>-563</v>
+        <v>-691</v>
       </c>
       <c r="AI3" t="n">
-        <v>-8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -830,31 +830,31 @@
         <v>1264</v>
       </c>
       <c r="D4" t="n">
-        <v>718</v>
+        <v>1159</v>
       </c>
       <c r="E4" t="n">
-        <v>56.8</v>
+        <v>91.69</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="I4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="J4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -866,31 +866,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="S4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
       <c r="T4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="U4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -902,28 +902,28 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="AC4" t="n">
         <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="AE4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
       <c r="AF4" t="n">
-        <v>-156</v>
+        <v>-226</v>
       </c>
       <c r="AG4" t="n">
-        <v>-26</v>
+        <v>52</v>
       </c>
       <c r="AH4" t="n">
-        <v>-156</v>
+        <v>-226</v>
       </c>
       <c r="AI4" t="n">
-        <v>-26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -941,31 +941,31 @@
         <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>4525</v>
+        <v>5498</v>
       </c>
       <c r="E5" t="n">
-        <v>93.11</v>
+        <v>113.13</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.35</v>
+        <v>7.13</v>
       </c>
       <c r="H5" t="n">
-        <v>1605</v>
+        <v>957</v>
       </c>
       <c r="I5" t="n">
-        <v>3789</v>
+        <v>4368</v>
       </c>
       <c r="J5" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -977,31 +977,31 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>6241</v>
+        <v>6487</v>
       </c>
       <c r="S5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
       <c r="T5" t="n">
-        <v>1605</v>
+        <v>959</v>
       </c>
       <c r="U5" t="n">
-        <v>3789</v>
+        <v>4368</v>
       </c>
       <c r="V5" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="W5" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="X5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1013,28 +1013,28 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6240</v>
+        <v>6487</v>
       </c>
       <c r="AE5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1381</v>
+        <v>-1627</v>
       </c>
       <c r="AG5" t="n">
-        <v>-25</v>
+        <v>68</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1380</v>
+        <v>-1627</v>
       </c>
       <c r="AI5" t="n">
-        <v>-25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1052,10 +1052,10 @@
         <v>2537</v>
       </c>
       <c r="D6" t="n">
-        <v>2343</v>
+        <v>2999</v>
       </c>
       <c r="E6" t="n">
-        <v>92.34999999999999</v>
+        <v>118.21</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1064,88 +1064,88 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>805</v>
+        <v>382</v>
       </c>
       <c r="I6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="J6" t="n">
+        <v>121</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22</v>
+      </c>
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="S6" t="n">
-        <v>2353</v>
+        <v>2924</v>
       </c>
       <c r="T6" t="n">
-        <v>806</v>
+        <v>383</v>
       </c>
       <c r="U6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="AE6" t="n">
-        <v>2352</v>
+        <v>2923</v>
       </c>
       <c r="AF6" t="n">
-        <v>-621</v>
+        <v>-769</v>
       </c>
       <c r="AG6" t="n">
-        <v>-10</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="n">
-        <v>-621</v>
+        <v>-769</v>
       </c>
       <c r="AI6" t="n">
-        <v>-9</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1163,31 +1163,31 @@
         <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>850</v>
       </c>
       <c r="E7" t="n">
-        <v>71.09999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>421</v>
+        <v>310</v>
       </c>
       <c r="I7" t="n">
-        <v>558</v>
+        <v>694</v>
       </c>
       <c r="J7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1199,31 +1199,31 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1158</v>
+      </c>
+      <c r="S7" t="n">
+        <v>832</v>
+      </c>
+      <c r="T7" t="n">
+        <v>310</v>
+      </c>
+      <c r="U7" t="n">
+        <v>694</v>
+      </c>
+      <c r="V7" t="n">
         <v>8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="S7" t="n">
-        <v>693</v>
-      </c>
-      <c r="T7" t="n">
-        <v>422</v>
-      </c>
-      <c r="U7" t="n">
-        <v>558</v>
-      </c>
-      <c r="V7" t="n">
-        <v>31</v>
-      </c>
       <c r="W7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1235,28 +1235,28 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="AE7" t="n">
-        <v>692</v>
+        <v>832</v>
       </c>
       <c r="AF7" t="n">
-        <v>-179</v>
+        <v>-203</v>
       </c>
       <c r="AG7" t="n">
-        <v>-14</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>-179</v>
+        <v>-203</v>
       </c>
       <c r="AI7" t="n">
-        <v>-13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1274,10 +1274,10 @@
         <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>634</v>
+        <v>813</v>
       </c>
       <c r="E8" t="n">
-        <v>80.15000000000001</v>
+        <v>102.78</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1286,88 +1286,88 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="I8" t="n">
-        <v>504</v>
+        <v>644</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S8" t="n">
+        <v>784</v>
+      </c>
+      <c r="T8" t="n">
+        <v>280</v>
+      </c>
+      <c r="U8" t="n">
+        <v>644</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>112</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1019</v>
-      </c>
-      <c r="S8" t="n">
-        <v>634</v>
-      </c>
-      <c r="T8" t="n">
-        <v>384</v>
-      </c>
-      <c r="U8" t="n">
-        <v>504</v>
-      </c>
-      <c r="V8" t="n">
-        <v>10</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1019</v>
+        <v>1065</v>
       </c>
       <c r="AE8" t="n">
-        <v>634</v>
+        <v>784</v>
       </c>
       <c r="AF8" t="n">
-        <v>-228</v>
+        <v>-274</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AH8" t="n">
-        <v>-228</v>
+        <v>-274</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1385,100 +1385,100 @@
         <v>3701</v>
       </c>
       <c r="D9" t="n">
-        <v>2493</v>
+        <v>3252</v>
       </c>
       <c r="E9" t="n">
-        <v>67.36</v>
+        <v>87.87</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="I9" t="n">
-        <v>1986</v>
+        <v>2443</v>
       </c>
       <c r="J9" t="n">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="S9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
       <c r="T9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="U9" t="n">
-        <v>1990</v>
+        <v>2443</v>
       </c>
       <c r="V9" t="n">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="W9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="AE9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
       <c r="AF9" t="n">
-        <v>-895</v>
+        <v>-1109</v>
       </c>
       <c r="AG9" t="n">
-        <v>-17</v>
+        <v>99</v>
       </c>
       <c r="AH9" t="n">
-        <v>-895</v>
+        <v>-1109</v>
       </c>
       <c r="AI9" t="n">
-        <v>-17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1496,100 +1496,100 @@
         <v>4982</v>
       </c>
       <c r="D10" t="n">
-        <v>3125</v>
+        <v>4497</v>
       </c>
       <c r="E10" t="n">
-        <v>62.73</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>9.629999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2813</v>
+        <v>1980</v>
       </c>
       <c r="I10" t="n">
-        <v>2427</v>
+        <v>3260</v>
       </c>
       <c r="J10" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5997</v>
+        <v>6348</v>
       </c>
       <c r="S10" t="n">
-        <v>3149</v>
+        <v>4331</v>
       </c>
       <c r="T10" t="n">
-        <v>2808</v>
+        <v>1980</v>
       </c>
       <c r="U10" t="n">
-        <v>2424</v>
+        <v>3260</v>
       </c>
       <c r="V10" t="n">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="W10" t="n">
         <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5997</v>
+        <v>6347</v>
       </c>
       <c r="AE10" t="n">
-        <v>3152</v>
+        <v>4330</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1015</v>
+        <v>-1366</v>
       </c>
       <c r="AG10" t="n">
-        <v>-24</v>
+        <v>166</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1015</v>
+        <v>-1365</v>
       </c>
       <c r="AI10" t="n">
-        <v>-27</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -1607,100 +1607,100 @@
         <v>6920</v>
       </c>
       <c r="D11" t="n">
-        <v>4339</v>
+        <v>5900</v>
       </c>
       <c r="E11" t="n">
-        <v>62.7</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>7.27</v>
+        <v>6.73</v>
       </c>
       <c r="H11" t="n">
-        <v>3560</v>
+        <v>2620</v>
       </c>
       <c r="I11" t="n">
-        <v>3868</v>
+        <v>5034</v>
       </c>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q11" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>456</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>8450</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5652</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2620</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5034</v>
+      </c>
+      <c r="V11" t="n">
+        <v>48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>176</v>
+      </c>
+      <c r="X11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="n">
-        <v>8064</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4368</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3560</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3868</v>
-      </c>
-      <c r="V11" t="n">
-        <v>28</v>
-      </c>
-      <c r="W11" t="n">
-        <v>136</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>542</v>
+      </c>
+      <c r="AC11" t="n">
         <v>6</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>456</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5</v>
-      </c>
       <c r="AD11" t="n">
-        <v>8064</v>
+        <v>8448</v>
       </c>
       <c r="AE11" t="n">
-        <v>4368</v>
+        <v>5652</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1144</v>
+        <v>-1530</v>
       </c>
       <c r="AG11" t="n">
-        <v>-29</v>
+        <v>248</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1144</v>
+        <v>-1528</v>
       </c>
       <c r="AI11" t="n">
-        <v>-29</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
@@ -1718,100 +1718,100 @@
         <v>4605</v>
       </c>
       <c r="D12" t="n">
-        <v>2969</v>
+        <v>3900</v>
       </c>
       <c r="E12" t="n">
-        <v>64.47</v>
+        <v>84.69</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2</v>
+        <v>7.56</v>
       </c>
       <c r="H12" t="n">
-        <v>2077</v>
+        <v>1416</v>
       </c>
       <c r="I12" t="n">
-        <v>2487</v>
+        <v>3241</v>
       </c>
       <c r="J12" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>453</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="S12" t="n">
-        <v>2983</v>
+        <v>3797</v>
       </c>
       <c r="T12" t="n">
-        <v>2077</v>
+        <v>1418</v>
       </c>
       <c r="U12" t="n">
-        <v>2487</v>
+        <v>3241</v>
       </c>
       <c r="V12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="W12" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="X12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>453</v>
+      </c>
+      <c r="AC12" t="n">
         <v>5</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>371</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
       <c r="AD12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="AE12" t="n">
-        <v>2983</v>
+        <v>3795</v>
       </c>
       <c r="AF12" t="n">
-        <v>-572</v>
+        <v>-756</v>
       </c>
       <c r="AG12" t="n">
-        <v>-14</v>
+        <v>103</v>
       </c>
       <c r="AH12" t="n">
-        <v>-572</v>
+        <v>-756</v>
       </c>
       <c r="AI12" t="n">
-        <v>-14</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1829,100 +1829,100 @@
         <v>2209</v>
       </c>
       <c r="D13" t="n">
-        <v>1255</v>
+        <v>1682</v>
       </c>
       <c r="E13" t="n">
-        <v>56.81</v>
+        <v>76.14</v>
       </c>
       <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>751</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86</v>
+      </c>
+      <c r="L13" t="n">
+        <v>70</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>7</v>
       </c>
-      <c r="G13" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1115</v>
-      </c>
-      <c r="I13" t="n">
-        <v>844</v>
-      </c>
-      <c r="J13" t="n">
-        <v>145</v>
-      </c>
-      <c r="K13" t="n">
-        <v>25</v>
-      </c>
-      <c r="L13" t="n">
-        <v>28</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R13" t="n">
-        <v>2406</v>
+        <v>2445</v>
       </c>
       <c r="S13" t="n">
-        <v>1266</v>
+        <v>1608</v>
       </c>
       <c r="T13" t="n">
-        <v>1115</v>
+        <v>751</v>
       </c>
       <c r="U13" t="n">
-        <v>841</v>
+        <v>1248</v>
       </c>
       <c r="V13" t="n">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AC13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>2406</v>
+        <v>2445</v>
       </c>
       <c r="AE13" t="n">
-        <v>1266</v>
+        <v>1608</v>
       </c>
       <c r="AF13" t="n">
-        <v>-197</v>
+        <v>-236</v>
       </c>
       <c r="AG13" t="n">
-        <v>-11</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="n">
-        <v>-197</v>
+        <v>-236</v>
       </c>
       <c r="AI13" t="n">
-        <v>-11</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -1940,100 +1940,100 @@
         <v>7057</v>
       </c>
       <c r="D14" t="n">
-        <v>6365</v>
+        <v>8435</v>
       </c>
       <c r="E14" t="n">
-        <v>90.19</v>
+        <v>119.53</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>12.28</v>
+        <v>4.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2948</v>
+        <v>1393</v>
       </c>
       <c r="I14" t="n">
-        <v>5564</v>
+        <v>7134</v>
       </c>
       <c r="J14" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>9558</v>
+        <v>9735</v>
       </c>
       <c r="S14" t="n">
-        <v>6511</v>
+        <v>8195</v>
       </c>
       <c r="T14" t="n">
-        <v>2682</v>
+        <v>1394</v>
       </c>
       <c r="U14" t="n">
-        <v>5561</v>
+        <v>7134</v>
       </c>
       <c r="V14" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="W14" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="AC14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>9203</v>
+        <v>9735</v>
       </c>
       <c r="AE14" t="n">
-        <v>6424</v>
+        <v>8195</v>
       </c>
       <c r="AF14" t="n">
-        <v>-2501</v>
+        <v>-2678</v>
       </c>
       <c r="AG14" t="n">
-        <v>-146</v>
+        <v>240</v>
       </c>
       <c r="AH14" t="n">
-        <v>-2146</v>
+        <v>-2678</v>
       </c>
       <c r="AI14" t="n">
-        <v>-59</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -2051,10 +2051,10 @@
         <v>911</v>
       </c>
       <c r="D15" t="n">
-        <v>868</v>
+        <v>1095</v>
       </c>
       <c r="E15" t="n">
-        <v>95.28</v>
+        <v>120.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2063,13 +2063,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="I15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2087,25 +2087,25 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="S15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
       <c r="T15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="U15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2123,28 +2123,28 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="AE15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
       <c r="AF15" t="n">
-        <v>-244</v>
+        <v>-279</v>
       </c>
       <c r="AG15" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>-244</v>
+        <v>-279</v>
       </c>
       <c r="AI15" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2162,10 +2162,10 @@
         <v>452</v>
       </c>
       <c r="D16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E16" t="n">
-        <v>87.17</v>
+        <v>89.38</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -2198,28 +2198,28 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="S16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="T16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="U16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
         <v>3</v>
@@ -2234,25 +2234,25 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AE16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="AF16" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
         <v>2416</v>
       </c>
       <c r="D17" t="n">
-        <v>1615</v>
+        <v>2133</v>
       </c>
       <c r="E17" t="n">
-        <v>66.84999999999999</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2285,22 +2285,22 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1162</v>
+        <v>815</v>
       </c>
       <c r="I17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
         <v>8</v>
@@ -2309,34 +2309,34 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2805</v>
+        <v>2921</v>
       </c>
       <c r="S17" t="n">
-        <v>1640</v>
+        <v>2106</v>
       </c>
       <c r="T17" t="n">
-        <v>1163</v>
+        <v>815</v>
       </c>
       <c r="U17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="V17" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
         <v>8</v>
@@ -2345,28 +2345,28 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="AC17" t="n">
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2804</v>
+        <v>2921</v>
       </c>
       <c r="AE17" t="n">
-        <v>1638</v>
+        <v>2106</v>
       </c>
       <c r="AF17" t="n">
-        <v>-389</v>
+        <v>-505</v>
       </c>
       <c r="AG17" t="n">
-        <v>-25</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
-        <v>-388</v>
+        <v>-505</v>
       </c>
       <c r="AI17" t="n">
-        <v>-23</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,177 +429,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,177 +417,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,177 +429,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -608,16 +620,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -695,13 +707,13 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>12</v>
       </c>
       <c r="AI2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -719,100 +731,100 @@
         <v>3567</v>
       </c>
       <c r="D3" t="n">
-        <v>3626</v>
+        <v>4426</v>
       </c>
       <c r="E3" t="n">
-        <v>101.65</v>
+        <v>124.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="H3" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>2752</v>
+        <v>3545</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="K3" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
-        <v>4258</v>
+        <v>4454</v>
       </c>
       <c r="S3" t="n">
-        <v>3560</v>
+        <v>4424</v>
       </c>
       <c r="T3" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="U3" t="n">
-        <v>2754</v>
+        <v>3533</v>
       </c>
       <c r="V3" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="W3" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="AC3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AD3" t="n">
-        <v>4258</v>
+        <v>4453</v>
       </c>
       <c r="AE3" t="n">
-        <v>3560</v>
+        <v>4423</v>
       </c>
       <c r="AF3" t="n">
-        <v>-691</v>
+        <v>-887</v>
       </c>
       <c r="AG3" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>-691</v>
+        <v>-886</v>
       </c>
       <c r="AI3" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -830,31 +842,31 @@
         <v>1264</v>
       </c>
       <c r="D4" t="n">
-        <v>1159</v>
+        <v>1358</v>
       </c>
       <c r="E4" t="n">
-        <v>91.69</v>
+        <v>107.44</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>273.97</v>
       </c>
       <c r="H4" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="I4" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -866,31 +878,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="S4" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
       <c r="T4" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="U4" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="W4" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -902,28 +914,28 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="AE4" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
       <c r="AF4" t="n">
-        <v>-226</v>
+        <v>-249</v>
       </c>
       <c r="AG4" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>-226</v>
+        <v>-249</v>
       </c>
       <c r="AI4" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -941,100 +953,100 @@
         <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>5498</v>
+        <v>6676</v>
       </c>
       <c r="E5" t="n">
-        <v>113.13</v>
+        <v>137.37</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>7.13</v>
+        <v>30.1</v>
       </c>
       <c r="H5" t="n">
-        <v>957</v>
+        <v>112</v>
       </c>
       <c r="I5" t="n">
-        <v>4368</v>
+        <v>5543</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="S5" t="n">
-        <v>5430</v>
+        <v>6662</v>
       </c>
       <c r="T5" t="n">
-        <v>959</v>
+        <v>113</v>
       </c>
       <c r="U5" t="n">
-        <v>4368</v>
+        <v>5543</v>
       </c>
       <c r="V5" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="W5" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="X5" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="AE5" t="n">
-        <v>5430</v>
+        <v>6661</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1627</v>
+        <v>-1935</v>
       </c>
       <c r="AG5" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1627</v>
+        <v>-1935</v>
       </c>
       <c r="AI5" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1052,10 +1064,10 @@
         <v>2537</v>
       </c>
       <c r="D6" t="n">
-        <v>2999</v>
+        <v>3521</v>
       </c>
       <c r="E6" t="n">
-        <v>118.21</v>
+        <v>138.79</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1064,88 +1076,88 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="J6" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="S6" t="n">
-        <v>2924</v>
+        <v>3521</v>
       </c>
       <c r="T6" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="V6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="AE6" t="n">
-        <v>2923</v>
+        <v>3521</v>
       </c>
       <c r="AF6" t="n">
-        <v>-769</v>
+        <v>-984</v>
       </c>
       <c r="AG6" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-769</v>
+        <v>-984</v>
       </c>
       <c r="AI6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1163,100 +1175,100 @@
         <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>850</v>
+        <v>1099</v>
       </c>
       <c r="E7" t="n">
-        <v>89.01000000000001</v>
+        <v>115.08</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>26.82</v>
       </c>
       <c r="H7" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="I7" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
         <v>16</v>
       </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="S7" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
       <c r="T7" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="U7" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
+        <v>7</v>
+      </c>
+      <c r="X7" t="n">
         <v>16</v>
       </c>
-      <c r="X7" t="n">
-        <v>9</v>
-      </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="AE7" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
       <c r="AF7" t="n">
-        <v>-203</v>
+        <v>-254</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="AH7" t="n">
-        <v>-203</v>
+        <v>-254</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -1274,10 +1286,10 @@
         <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>813</v>
+        <v>1092</v>
       </c>
       <c r="E8" t="n">
-        <v>102.78</v>
+        <v>138.05</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1286,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="I8" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1310,28 +1322,28 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="S8" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
       <c r="T8" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="U8" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1346,28 +1358,28 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="AE8" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
       <c r="AF8" t="n">
-        <v>-274</v>
+        <v>-342</v>
       </c>
       <c r="AG8" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>-274</v>
+        <v>-342</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1385,100 +1397,100 @@
         <v>3701</v>
       </c>
       <c r="D9" t="n">
-        <v>3252</v>
+        <v>4447</v>
       </c>
       <c r="E9" t="n">
-        <v>87.87</v>
+        <v>120.16</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>84.42999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1630</v>
+        <v>745</v>
       </c>
       <c r="I9" t="n">
-        <v>2443</v>
+        <v>3557</v>
       </c>
       <c r="J9" t="n">
-        <v>289</v>
+        <v>205</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="S9" t="n">
-        <v>3153</v>
+        <v>4402</v>
       </c>
       <c r="T9" t="n">
-        <v>1630</v>
+        <v>748</v>
       </c>
       <c r="U9" t="n">
-        <v>2443</v>
+        <v>3555</v>
       </c>
       <c r="V9" t="n">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="W9" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="AE9" t="n">
-        <v>3153</v>
+        <v>4399</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1109</v>
+        <v>-1498</v>
       </c>
       <c r="AG9" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1109</v>
+        <v>-1498</v>
       </c>
       <c r="AI9" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1496,100 +1508,100 @@
         <v>4982</v>
       </c>
       <c r="D10" t="n">
-        <v>4497</v>
+        <v>5916</v>
       </c>
       <c r="E10" t="n">
-        <v>90.26000000000001</v>
+        <v>118.75</v>
       </c>
       <c r="F10" t="n">
+        <v>101</v>
+      </c>
+      <c r="G10" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>742</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4117</v>
+      </c>
+      <c r="J10" t="n">
+        <v>780</v>
+      </c>
+      <c r="K10" t="n">
+        <v>113</v>
+      </c>
+      <c r="L10" t="n">
+        <v>336</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33</v>
+      </c>
+      <c r="N10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1980</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3260</v>
-      </c>
-      <c r="J10" t="n">
-        <v>296</v>
-      </c>
-      <c r="K10" t="n">
-        <v>37</v>
-      </c>
-      <c r="L10" t="n">
-        <v>198</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>6348</v>
+        <v>6749</v>
       </c>
       <c r="S10" t="n">
-        <v>4331</v>
+        <v>5894</v>
       </c>
       <c r="T10" t="n">
-        <v>1980</v>
+        <v>742</v>
       </c>
       <c r="U10" t="n">
-        <v>3260</v>
+        <v>4117</v>
       </c>
       <c r="V10" t="n">
-        <v>295</v>
+        <v>780</v>
       </c>
       <c r="W10" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="X10" t="n">
-        <v>198</v>
+        <v>335</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>6347</v>
+        <v>6749</v>
       </c>
       <c r="AE10" t="n">
-        <v>4330</v>
+        <v>5894</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1366</v>
+        <v>-1767</v>
       </c>
       <c r="AG10" t="n">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1365</v>
+        <v>-1767</v>
       </c>
       <c r="AI10" t="n">
-        <v>167</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1607,100 +1619,100 @@
         <v>6920</v>
       </c>
       <c r="D11" t="n">
-        <v>5900</v>
+        <v>7979</v>
       </c>
       <c r="E11" t="n">
-        <v>85.26000000000001</v>
+        <v>115.3</v>
       </c>
       <c r="F11" t="n">
+        <v>94</v>
+      </c>
+      <c r="G11" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="H11" t="n">
+        <v>980</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6975</v>
+      </c>
+      <c r="J11" t="n">
+        <v>281</v>
+      </c>
+      <c r="K11" t="n">
+        <v>95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>42</v>
+      </c>
+      <c r="M11" t="n">
         <v>7</v>
       </c>
-      <c r="G11" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2620</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5034</v>
-      </c>
-      <c r="J11" t="n">
-        <v>48</v>
-      </c>
-      <c r="K11" t="n">
-        <v>178</v>
-      </c>
-      <c r="L11" t="n">
-        <v>15</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>8450</v>
+        <v>8991</v>
       </c>
       <c r="S11" t="n">
-        <v>5652</v>
+        <v>7916</v>
       </c>
       <c r="T11" t="n">
-        <v>2620</v>
+        <v>981</v>
       </c>
       <c r="U11" t="n">
-        <v>5034</v>
+        <v>6975</v>
       </c>
       <c r="V11" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="W11" t="n">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>8448</v>
+        <v>8991</v>
       </c>
       <c r="AE11" t="n">
-        <v>5652</v>
+        <v>7915</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1530</v>
+        <v>-2071</v>
       </c>
       <c r="AG11" t="n">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1528</v>
+        <v>-2071</v>
       </c>
       <c r="AI11" t="n">
-        <v>248</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -1718,100 +1730,100 @@
         <v>4605</v>
       </c>
       <c r="D12" t="n">
-        <v>3900</v>
+        <v>5094</v>
       </c>
       <c r="E12" t="n">
-        <v>84.69</v>
+        <v>110.62</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="G12" t="n">
-        <v>7.56</v>
+        <v>228.63</v>
       </c>
       <c r="H12" t="n">
-        <v>1416</v>
+        <v>432</v>
       </c>
       <c r="I12" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="J12" t="n">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="K12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="S12" t="n">
-        <v>3797</v>
+        <v>5057</v>
       </c>
       <c r="T12" t="n">
-        <v>1418</v>
+        <v>434</v>
       </c>
       <c r="U12" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="V12" t="n">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="W12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="AE12" t="n">
-        <v>3795</v>
+        <v>5055</v>
       </c>
       <c r="AF12" t="n">
-        <v>-756</v>
+        <v>-1029</v>
       </c>
       <c r="AG12" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="AH12" t="n">
-        <v>-756</v>
+        <v>-1029</v>
       </c>
       <c r="AI12" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -1829,34 +1841,34 @@
         <v>2209</v>
       </c>
       <c r="D13" t="n">
-        <v>1682</v>
+        <v>2250</v>
       </c>
       <c r="E13" t="n">
-        <v>76.14</v>
+        <v>101.86</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1</v>
+        <v>93.7</v>
       </c>
       <c r="H13" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="I13" t="n">
-        <v>1250</v>
+        <v>1652</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="K13" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="L13" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -1865,34 +1877,34 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="S13" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
       <c r="T13" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="U13" t="n">
-        <v>1248</v>
+        <v>1652</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="W13" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="X13" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
@@ -1901,28 +1913,28 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD13" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="AE13" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
       <c r="AF13" t="n">
-        <v>-236</v>
+        <v>-276</v>
       </c>
       <c r="AG13" t="n">
-        <v>74</v>
+        <v>-7</v>
       </c>
       <c r="AH13" t="n">
-        <v>-236</v>
+        <v>-276</v>
       </c>
       <c r="AI13" t="n">
-        <v>74</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="14">
@@ -1940,100 +1952,100 @@
         <v>7057</v>
       </c>
       <c r="D14" t="n">
-        <v>8435</v>
+        <v>10213</v>
       </c>
       <c r="E14" t="n">
-        <v>119.53</v>
+        <v>144.72</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>4.55</v>
+        <v>41.72</v>
       </c>
       <c r="H14" t="n">
-        <v>1393</v>
+        <v>149</v>
       </c>
       <c r="I14" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="J14" t="n">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="K14" t="n">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="S14" t="n">
-        <v>8195</v>
+        <v>10172</v>
       </c>
       <c r="T14" t="n">
-        <v>1394</v>
+        <v>149</v>
       </c>
       <c r="U14" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="V14" t="n">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="W14" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="AE14" t="n">
-        <v>8195</v>
+        <v>10171</v>
       </c>
       <c r="AF14" t="n">
-        <v>-2678</v>
+        <v>-3322</v>
       </c>
       <c r="AG14" t="n">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="AH14" t="n">
-        <v>-2678</v>
+        <v>-3322</v>
       </c>
       <c r="AI14" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -2051,10 +2063,10 @@
         <v>911</v>
       </c>
       <c r="D15" t="n">
-        <v>1095</v>
+        <v>1209</v>
       </c>
       <c r="E15" t="n">
-        <v>120.2</v>
+        <v>132.71</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2063,13 +2075,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2081,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2093,19 +2105,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="S15" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
       <c r="T15" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="V15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2117,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2129,22 +2141,22 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="AE15" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
       <c r="AF15" t="n">
-        <v>-279</v>
+        <v>-304</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AH15" t="n">
-        <v>-279</v>
+        <v>-304</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="16">
@@ -2162,31 +2174,31 @@
         <v>452</v>
       </c>
       <c r="D16" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="E16" t="n">
-        <v>89.38</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>23.59</v>
       </c>
       <c r="H16" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="I16" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2204,25 +2216,25 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="S16" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="T16" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="U16" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2240,19 +2252,19 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="AE16" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="AF16" t="n">
-        <v>-174</v>
+        <v>-184</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-174</v>
+        <v>-184</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2273,10 +2285,10 @@
         <v>2416</v>
       </c>
       <c r="D17" t="n">
-        <v>2133</v>
+        <v>2755</v>
       </c>
       <c r="E17" t="n">
-        <v>88.29000000000001</v>
+        <v>114.03</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2285,88 +2297,88 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>815</v>
+        <v>275</v>
       </c>
       <c r="I17" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="J17" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>516</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>24</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>492</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
       <c r="R17" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="S17" t="n">
-        <v>2106</v>
+        <v>2734</v>
       </c>
       <c r="T17" t="n">
-        <v>815</v>
+        <v>276</v>
       </c>
       <c r="U17" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="V17" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>516</v>
+      </c>
+      <c r="AC17" t="n">
         <v>4</v>
       </c>
-      <c r="Y17" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>492</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3</v>
-      </c>
       <c r="AD17" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="AE17" t="n">
-        <v>2106</v>
+        <v>2733</v>
       </c>
       <c r="AF17" t="n">
-        <v>-505</v>
+        <v>-593</v>
       </c>
       <c r="AG17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>-505</v>
+        <v>-593</v>
       </c>
       <c r="AI17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_PROGRES PENDATAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,177 +417,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -620,16 +608,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>58.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -707,13 +695,13 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>12</v>
       </c>
       <c r="AI2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -731,100 +719,100 @@
         <v>3567</v>
       </c>
       <c r="D3" t="n">
-        <v>4426</v>
+        <v>3626</v>
       </c>
       <c r="E3" t="n">
-        <v>124.08</v>
+        <v>101.65</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="I3" t="n">
-        <v>3545</v>
+        <v>2752</v>
       </c>
       <c r="J3" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>4454</v>
+        <v>4258</v>
       </c>
       <c r="S3" t="n">
-        <v>4424</v>
+        <v>3560</v>
       </c>
       <c r="T3" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="U3" t="n">
-        <v>3533</v>
+        <v>2754</v>
       </c>
       <c r="V3" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="AC3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>4453</v>
+        <v>4258</v>
       </c>
       <c r="AE3" t="n">
-        <v>4423</v>
+        <v>3560</v>
       </c>
       <c r="AF3" t="n">
-        <v>-887</v>
+        <v>-691</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="AH3" t="n">
-        <v>-886</v>
+        <v>-691</v>
       </c>
       <c r="AI3" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -842,31 +830,31 @@
         <v>1264</v>
       </c>
       <c r="D4" t="n">
-        <v>1358</v>
+        <v>1159</v>
       </c>
       <c r="E4" t="n">
-        <v>107.44</v>
+        <v>91.69</v>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>273.97</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="I4" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -878,31 +866,31 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="S4" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
       <c r="T4" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="U4" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -914,28 +902,28 @@
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="AE4" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
       <c r="AF4" t="n">
-        <v>-249</v>
+        <v>-226</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="AH4" t="n">
-        <v>-249</v>
+        <v>-226</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -953,100 +941,100 @@
         <v>4860</v>
       </c>
       <c r="D5" t="n">
-        <v>6676</v>
+        <v>5498</v>
       </c>
       <c r="E5" t="n">
-        <v>137.37</v>
+        <v>113.13</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>30.1</v>
+        <v>7.13</v>
       </c>
       <c r="H5" t="n">
-        <v>112</v>
+        <v>957</v>
       </c>
       <c r="I5" t="n">
-        <v>5543</v>
+        <v>4368</v>
       </c>
       <c r="J5" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="S5" t="n">
-        <v>6662</v>
+        <v>5430</v>
       </c>
       <c r="T5" t="n">
-        <v>113</v>
+        <v>959</v>
       </c>
       <c r="U5" t="n">
-        <v>5543</v>
+        <v>4368</v>
       </c>
       <c r="V5" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="W5" t="n">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="X5" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="AE5" t="n">
-        <v>6661</v>
+        <v>5430</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1935</v>
+        <v>-1627</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1935</v>
+        <v>-1627</v>
       </c>
       <c r="AI5" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1064,10 +1052,10 @@
         <v>2537</v>
       </c>
       <c r="D6" t="n">
-        <v>3521</v>
+        <v>2999</v>
       </c>
       <c r="E6" t="n">
-        <v>138.79</v>
+        <v>118.21</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1076,88 +1064,88 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="I6" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="S6" t="n">
-        <v>3521</v>
+        <v>2924</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="U6" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="AE6" t="n">
-        <v>3521</v>
+        <v>2923</v>
       </c>
       <c r="AF6" t="n">
-        <v>-984</v>
+        <v>-769</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="n">
-        <v>-984</v>
+        <v>-769</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1175,100 +1163,100 @@
         <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>1099</v>
+        <v>850</v>
       </c>
       <c r="E7" t="n">
-        <v>115.08</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>26.82</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="I7" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="S7" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
       <c r="T7" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="U7" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="AE7" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
       <c r="AF7" t="n">
-        <v>-254</v>
+        <v>-203</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>-254</v>
+        <v>-203</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1286,10 +1274,10 @@
         <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>1092</v>
+        <v>813</v>
       </c>
       <c r="E8" t="n">
-        <v>138.05</v>
+        <v>102.78</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1298,16 +1286,16 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="I8" t="n">
-        <v>912</v>
+        <v>644</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1322,28 +1310,28 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="S8" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
       <c r="T8" t="n">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="U8" t="n">
-        <v>912</v>
+        <v>644</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1358,28 +1346,28 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="AE8" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
       <c r="AF8" t="n">
-        <v>-342</v>
+        <v>-274</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AH8" t="n">
-        <v>-342</v>
+        <v>-274</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1397,100 +1385,100 @@
         <v>3701</v>
       </c>
       <c r="D9" t="n">
-        <v>4447</v>
+        <v>3252</v>
       </c>
       <c r="E9" t="n">
-        <v>120.16</v>
+        <v>87.87</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>84.42999999999999</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>745</v>
+        <v>1630</v>
       </c>
       <c r="I9" t="n">
-        <v>3557</v>
+        <v>2443</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="S9" t="n">
-        <v>4402</v>
+        <v>3153</v>
       </c>
       <c r="T9" t="n">
-        <v>748</v>
+        <v>1630</v>
       </c>
       <c r="U9" t="n">
-        <v>3555</v>
+        <v>2443</v>
       </c>
       <c r="V9" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="W9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AC9" t="n">
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="AE9" t="n">
-        <v>4399</v>
+        <v>3153</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1498</v>
+        <v>-1109</v>
       </c>
       <c r="AG9" t="n">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1498</v>
+        <v>-1109</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1508,100 +1496,100 @@
         <v>4982</v>
       </c>
       <c r="D10" t="n">
-        <v>5916</v>
+        <v>4497</v>
       </c>
       <c r="E10" t="n">
-        <v>118.75</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>125.1</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="I10" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="J10" t="n">
-        <v>780</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="M10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>6749</v>
+        <v>6348</v>
       </c>
       <c r="S10" t="n">
-        <v>5894</v>
+        <v>4331</v>
       </c>
       <c r="T10" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="U10" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="V10" t="n">
-        <v>780</v>
+        <v>295</v>
       </c>
       <c r="W10" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>6749</v>
+        <v>6347</v>
       </c>
       <c r="AE10" t="n">
-        <v>5894</v>
+        <v>4330</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1767</v>
+        <v>-1366</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1767</v>
+        <v>-1365</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -1619,100 +1607,100 @@
         <v>6920</v>
       </c>
       <c r="D11" t="n">
-        <v>7979</v>
+        <v>5900</v>
       </c>
       <c r="E11" t="n">
-        <v>115.3</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>97.53</v>
+        <v>6.73</v>
       </c>
       <c r="H11" t="n">
-        <v>980</v>
+        <v>2620</v>
       </c>
       <c r="I11" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="J11" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>8991</v>
+        <v>8450</v>
       </c>
       <c r="S11" t="n">
-        <v>7916</v>
+        <v>5652</v>
       </c>
       <c r="T11" t="n">
-        <v>981</v>
+        <v>2620</v>
       </c>
       <c r="U11" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="V11" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="W11" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
         <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>8991</v>
+        <v>8448</v>
       </c>
       <c r="AE11" t="n">
-        <v>7915</v>
+        <v>5652</v>
       </c>
       <c r="AF11" t="n">
-        <v>-2071</v>
+        <v>-1530</v>
       </c>
       <c r="AG11" t="n">
-        <v>63</v>
+        <v>248</v>
       </c>
       <c r="AH11" t="n">
-        <v>-2071</v>
+        <v>-1528</v>
       </c>
       <c r="AI11" t="n">
-        <v>64</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
@@ -1730,100 +1718,100 @@
         <v>4605</v>
       </c>
       <c r="D12" t="n">
-        <v>5094</v>
+        <v>3900</v>
       </c>
       <c r="E12" t="n">
-        <v>110.62</v>
+        <v>84.69</v>
       </c>
       <c r="F12" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>228.63</v>
+        <v>7.56</v>
       </c>
       <c r="H12" t="n">
-        <v>432</v>
+        <v>1416</v>
       </c>
       <c r="I12" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="J12" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="S12" t="n">
-        <v>5057</v>
+        <v>3797</v>
       </c>
       <c r="T12" t="n">
-        <v>434</v>
+        <v>1418</v>
       </c>
       <c r="U12" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="V12" t="n">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="W12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="AC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="AE12" t="n">
-        <v>5055</v>
+        <v>3795</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1029</v>
+        <v>-756</v>
       </c>
       <c r="AG12" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1029</v>
+        <v>-756</v>
       </c>
       <c r="AI12" t="n">
-        <v>39</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1841,34 +1829,34 @@
         <v>2209</v>
       </c>
       <c r="D13" t="n">
-        <v>2250</v>
+        <v>1682</v>
       </c>
       <c r="E13" t="n">
-        <v>101.86</v>
+        <v>76.14</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>93.7</v>
+        <v>9.1</v>
       </c>
       <c r="H13" t="n">
-        <v>174</v>
+        <v>751</v>
       </c>
       <c r="I13" t="n">
-        <v>1652</v>
+        <v>1250</v>
       </c>
       <c r="J13" t="n">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L13" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="M13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -1877,34 +1865,34 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R13" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="S13" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
       <c r="T13" t="n">
-        <v>174</v>
+        <v>751</v>
       </c>
       <c r="U13" t="n">
-        <v>1652</v>
+        <v>1248</v>
       </c>
       <c r="V13" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="X13" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>7</v>
@@ -1913,28 +1901,28 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AC13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="AE13" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
       <c r="AF13" t="n">
-        <v>-276</v>
+        <v>-236</v>
       </c>
       <c r="AG13" t="n">
-        <v>-7</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="n">
-        <v>-276</v>
+        <v>-236</v>
       </c>
       <c r="AI13" t="n">
-        <v>-7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -1952,100 +1940,100 @@
         <v>7057</v>
       </c>
       <c r="D14" t="n">
-        <v>10213</v>
+        <v>8435</v>
       </c>
       <c r="E14" t="n">
-        <v>144.72</v>
+        <v>119.53</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>41.72</v>
+        <v>4.55</v>
       </c>
       <c r="H14" t="n">
-        <v>149</v>
+        <v>1393</v>
       </c>
       <c r="I14" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="J14" t="n">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="K14" t="n">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="S14" t="n">
-        <v>10172</v>
+        <v>8195</v>
       </c>
       <c r="T14" t="n">
-        <v>149</v>
+        <v>1394</v>
       </c>
       <c r="U14" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="V14" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="W14" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="AE14" t="n">
-        <v>10171</v>
+        <v>8195</v>
       </c>
       <c r="AF14" t="n">
-        <v>-3322</v>
+        <v>-2678</v>
       </c>
       <c r="AG14" t="n">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c r="AH14" t="n">
-        <v>-3322</v>
+        <v>-2678</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2051,10 @@
         <v>911</v>
       </c>
       <c r="D15" t="n">
-        <v>1209</v>
+        <v>1095</v>
       </c>
       <c r="E15" t="n">
-        <v>132.71</v>
+        <v>120.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2075,13 +2063,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I15" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2093,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2105,19 +2093,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="S15" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="U15" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2129,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2141,22 +2129,22 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="AE15" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
       <c r="AF15" t="n">
-        <v>-304</v>
+        <v>-279</v>
       </c>
       <c r="AG15" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>-304</v>
+        <v>-279</v>
       </c>
       <c r="AI15" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2174,31 +2162,31 @@
         <v>452</v>
       </c>
       <c r="D16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="E16" t="n">
-        <v>96.23999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>23.59</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="I16" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2216,25 +2204,25 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="S16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="T16" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="U16" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2252,19 +2240,19 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="AE16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="AF16" t="n">
-        <v>-184</v>
+        <v>-174</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-184</v>
+        <v>-174</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2285,10 +2273,10 @@
         <v>2416</v>
       </c>
       <c r="D17" t="n">
-        <v>2755</v>
+        <v>2133</v>
       </c>
       <c r="E17" t="n">
-        <v>114.03</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2297,88 +2285,88 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>275</v>
+        <v>815</v>
       </c>
       <c r="I17" t="n">
-        <v>2176</v>
+        <v>1522</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2921</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2106</v>
+      </c>
+      <c r="T17" t="n">
+        <v>815</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1522</v>
+      </c>
+      <c r="V17" t="n">
+        <v>53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>3009</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2734</v>
-      </c>
-      <c r="T17" t="n">
-        <v>276</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2176</v>
-      </c>
-      <c r="V17" t="n">
-        <v>10</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>10</v>
-      </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3009</v>
+        <v>2921</v>
       </c>
       <c r="AE17" t="n">
-        <v>2733</v>
+        <v>2106</v>
       </c>
       <c r="AF17" t="n">
-        <v>-593</v>
+        <v>-505</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
-        <v>-593</v>
+        <v>-505</v>
       </c>
       <c r="AI17" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
